--- a/Modele/resultat/excel/resultats_XGBoost_preprocessed_iris_dataset.xlsx
+++ b/Modele/resultat/excel/resultats_XGBoost_preprocessed_iris_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,23 +516,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D2" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F2" t="n">
         <v>20</v>
       </c>
       <c r="G2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -545,27 +545,27 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0.676984126984127</v>
       </c>
       <c r="M2" t="n">
-        <v>0.05</v>
+        <v>0.32</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>{'n_estimators': 63, 'max_depth': 11, 'learning_rate': 0.039012056558080266}</t>
+          <t>{'n_estimators': 318, 'max_depth': 5, 'learning_rate': 0.04571287152360498}</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0.676984126984127</v>
       </c>
     </row>
     <row r="3">
@@ -574,23 +574,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="D3" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F3" t="n">
         <v>20</v>
       </c>
       <c r="G3" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -603,27 +603,27 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="K3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.7050427350427351</v>
       </c>
       <c r="M3" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>{'n_estimators': 191, 'max_depth': 2, 'learning_rate': 0.11131765858451852}</t>
+          <t>{'n_estimators': 185, 'max_depth': 17, 'learning_rate': 0.060917131696849126}</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.7050427350427351</v>
       </c>
     </row>
     <row r="4">
@@ -632,23 +632,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D4" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F4" t="n">
         <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -661,27 +661,27 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.6618055555555554</v>
       </c>
       <c r="M4" t="n">
-        <v>0.11</v>
+        <v>0.24</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>{'n_estimators': 255, 'max_depth': 2, 'learning_rate': 0.039054671123555394}</t>
+          <t>{'n_estimators': 276, 'max_depth': 17, 'learning_rate': 0.10917593170396998}</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0.6618055555555554</v>
       </c>
     </row>
     <row r="5">
@@ -690,23 +690,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D5" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F5" t="n">
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -719,27 +719,27 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.5785714285714286</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>{'n_estimators': 140, 'max_depth': 18, 'learning_rate': 0.01861528223399937}</t>
+          <t>{'n_estimators': 217, 'max_depth': 13, 'learning_rate': 0.018586636433117594}</t>
         </is>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.739084249084249</v>
       </c>
     </row>
     <row r="6">
@@ -748,23 +748,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>0.49</v>
       </c>
       <c r="D6" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F6" t="n">
         <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -777,27 +777,27 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>{'n_estimators': 408, 'max_depth': 11, 'learning_rate': 0.06338272829415083}</t>
+          <t>{'n_estimators': 129, 'max_depth': 6, 'learning_rate': 0.1333432286510667}</t>
         </is>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="7">
@@ -806,23 +806,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="D7" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E7" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F7" t="n">
         <v>20</v>
       </c>
       <c r="G7" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -835,27 +835,27 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>{'n_estimators': 239, 'max_depth': 5, 'learning_rate': 0.014427687576865637}</t>
+          <t>{'n_estimators': 485, 'max_depth': 4, 'learning_rate': 0.03982591136434708}</t>
         </is>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8">
@@ -864,23 +864,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="D8" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E8" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F8" t="n">
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -893,27 +893,27 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.829454205924794</v>
       </c>
       <c r="M8" t="n">
-        <v>0.12</v>
+        <v>0.24</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>{'n_estimators': 372, 'max_depth': 6, 'learning_rate': 0.12326714714593626}</t>
+          <t>{'n_estimators': 253, 'max_depth': 11, 'learning_rate': 0.06981621185619925}</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0.8645191409897292</v>
       </c>
     </row>
     <row r="9">
@@ -922,23 +922,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="D9" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E9" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -951,27 +951,27 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="K9" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.8298997493734336</v>
       </c>
       <c r="M9" t="n">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>{'n_estimators': 457, 'max_depth': 11, 'learning_rate': 0.017349223843240388}</t>
+          <t>{'n_estimators': 499, 'max_depth': 2, 'learning_rate': 0.012562857704949063}</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0.8298997493734336</v>
       </c>
     </row>
     <row r="10">
@@ -980,23 +980,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="D10" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E10" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F10" t="n">
         <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1009,27 +1009,27 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.8960127591706538</v>
       </c>
       <c r="M10" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>{'n_estimators': 75, 'max_depth': 9, 'learning_rate': 0.024332349541696306}</t>
+          <t>{'n_estimators': 108, 'max_depth': 14, 'learning_rate': 0.0353224711469667}</t>
         </is>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0.8960127591706538</v>
       </c>
     </row>
     <row r="11">
@@ -1038,23 +1038,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="D11" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F11" t="n">
         <v>20</v>
       </c>
       <c r="G11" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1067,27 +1067,27 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.8949832775919732</v>
       </c>
       <c r="M11" t="n">
-        <v>0.11</v>
+        <v>0.32</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>{'n_estimators': 238, 'max_depth': 12, 'learning_rate': 0.06286561722257694}</t>
+          <t>{'n_estimators': 418, 'max_depth': 6, 'learning_rate': 0.061370557816162956}</t>
         </is>
       </c>
       <c r="O11" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.8949832775919732</v>
       </c>
     </row>
     <row r="12">
@@ -1096,23 +1096,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>0.58</v>
       </c>
       <c r="D12" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E12" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>20</v>
       </c>
       <c r="G12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1125,27 +1125,27 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="K12" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.9321969696969696</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>{'n_estimators': 356, 'max_depth': 19, 'learning_rate': 0.036821249866359596}</t>
+          <t>{'n_estimators': 267, 'max_depth': 8, 'learning_rate': 0.12179941678153167}</t>
         </is>
       </c>
       <c r="O12" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0.9321969696969696</v>
       </c>
     </row>
     <row r="13">
@@ -1154,23 +1154,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="D13" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E13" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F13" t="n">
         <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1183,27 +1183,27 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.832463768115942</v>
       </c>
       <c r="M13" t="n">
-        <v>0.08</v>
+        <v>0.36</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>{'n_estimators': 171, 'max_depth': 6, 'learning_rate': 0.22441322406962158}</t>
+          <t>{'n_estimators': 411, 'max_depth': 19, 'learning_rate': 0.164100524290095}</t>
         </is>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0.832463768115942</v>
       </c>
     </row>
     <row r="14">
@@ -1212,23 +1212,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E14" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F14" t="n">
         <v>20</v>
       </c>
       <c r="G14" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1241,27 +1241,27 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.966280193236715</v>
       </c>
       <c r="M14" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>{'n_estimators': 457, 'max_depth': 6, 'learning_rate': 0.015303016027081482}</t>
+          <t>{'n_estimators': 61, 'max_depth': 16, 'learning_rate': 0.012958494864027247}</t>
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0.966280193236715</v>
       </c>
     </row>
     <row r="15">
@@ -1270,23 +1270,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E15" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F15" t="n">
         <v>20</v>
       </c>
       <c r="G15" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1299,27 +1299,27 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="K15" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0.8639730639730641</v>
       </c>
       <c r="M15" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>{'n_estimators': 248, 'max_depth': 7, 'learning_rate': 0.015658420482969594}</t>
+          <t>{'n_estimators': 94, 'max_depth': 18, 'learning_rate': 0.29961632304266905}</t>
         </is>
       </c>
       <c r="O15" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0.8639730639730641</v>
       </c>
     </row>
     <row r="16">
@@ -1328,23 +1328,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="D16" t="n">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="E16" t="n">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="F16" t="n">
         <v>20</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1357,52 +1357,52 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="K16" t="n">
-        <v>0.95</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9503836317135551</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>{'n_estimators': 247, 'max_depth': 17, 'learning_rate': 0.0212961643837513}</t>
+          <t>{'n_estimators': 261, 'max_depth': 11, 'learning_rate': 0.12776975740269328}</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0.95</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9503836317135551</v>
+        <v>0.9666666666666667</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.02</v>
+        <v>0.73</v>
       </c>
       <c r="D17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E17" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F17" t="n">
         <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1415,52 +1415,52 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="K17" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.9001790281329922</v>
       </c>
       <c r="M17" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>{'n_estimators': 85, 'max_depth': 13, 'learning_rate': 0.14450687175170543}</t>
+          <t>{'n_estimators': 109, 'max_depth': 3, 'learning_rate': 0.2828176236290519}</t>
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0.95</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.9332301341589267</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.01</v>
+        <v>0.51</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F18" t="n">
         <v>20</v>
       </c>
       <c r="G18" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1473,20 +1473,20 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>0.04</v>
+        <v>0.1</v>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L18" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="M18" t="n">
-        <v>0.13</v>
+        <v>0.4</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>{'n_estimators': 378, 'max_depth': 13, 'learning_rate': 0.21053608499156798}</t>
+          <t>{'n_estimators': 389, 'max_depth': 9, 'learning_rate': 0.012559097392204885}</t>
         </is>
       </c>
       <c r="O18" t="n">
@@ -1498,27 +1498,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F19" t="n">
         <v>20</v>
       </c>
       <c r="G19" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1531,52 +1531,52 @@
         </is>
       </c>
       <c r="J19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="M19" t="n">
         <v>0.05</v>
       </c>
-      <c r="K19" t="n">
-        <v>1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.11</v>
-      </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>{'n_estimators': 303, 'max_depth': 20, 'learning_rate': 0.011932717211783385}</t>
+          <t>{'n_estimators': 58, 'max_depth': 9, 'learning_rate': 0.22542186462607916}</t>
         </is>
       </c>
       <c r="O19" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F20" t="n">
         <v>20</v>
       </c>
       <c r="G20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1589,52 +1589,52 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>0.9665141113653699</v>
       </c>
       <c r="M20" t="n">
-        <v>0.14</v>
+        <v>0.4</v>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>{'n_estimators': 455, 'max_depth': 11, 'learning_rate': 0.12188474802561411}</t>
+          <t>{'n_estimators': 401, 'max_depth': 20, 'learning_rate': 0.08585649695109716}</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0.9665141113653699</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.01</v>
+        <v>0.54</v>
       </c>
       <c r="D21" t="n">
         <v>16</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F21" t="n">
         <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1647,52 +1647,52 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0.9664109121909633</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>{'n_estimators': 331, 'max_depth': 10, 'learning_rate': 0.28393408295796074}</t>
+          <t>{'n_estimators': 351, 'max_depth': 11, 'learning_rate': 0.035589090118508415}</t>
         </is>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0.9664109121909633</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="D22" t="n">
         <v>16</v>
       </c>
       <c r="E22" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F22" t="n">
         <v>20</v>
       </c>
       <c r="G22" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -1705,52 +1705,52 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="K22" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L22" t="n">
-        <v>1</v>
+        <v>0.8651461988304092</v>
       </c>
       <c r="M22" t="n">
-        <v>0.04</v>
+        <v>0.35</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>{'n_estimators': 64, 'max_depth': 7, 'learning_rate': 0.029258391409987268}</t>
+          <t>{'n_estimators': 467, 'max_depth': 2, 'learning_rate': 0.08423845506417767}</t>
         </is>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0.8651461988304092</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="D23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E23" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F23" t="n">
         <v>20</v>
       </c>
       <c r="G23" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -1763,52 +1763,52 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="K23" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L23" t="n">
-        <v>1</v>
+        <v>0.8996078431372548</v>
       </c>
       <c r="M23" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>{'n_estimators': 463, 'max_depth': 3, 'learning_rate': 0.06946036577149767}</t>
+          <t>{'n_estimators': 244, 'max_depth': 3, 'learning_rate': 0.1582043868957616}</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P23" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.01</v>
+        <v>0.47</v>
       </c>
       <c r="D24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F24" t="n">
         <v>20</v>
       </c>
       <c r="G24" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -1821,52 +1821,52 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="K24" t="n">
-        <v>0.95</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L24" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.8648809523809523</v>
       </c>
       <c r="M24" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>{'n_estimators': 423, 'max_depth': 5, 'learning_rate': 0.02586176495905194}</t>
+          <t>{'n_estimators': 252, 'max_depth': 17, 'learning_rate': 0.038249581751356204}</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0.95</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9493333333333334</v>
+        <v>0.8648809523809523</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="D25" t="n">
         <v>16</v>
       </c>
       <c r="E25" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F25" t="n">
         <v>20</v>
       </c>
       <c r="G25" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -1879,52 +1879,52 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0.8649350649350649</v>
       </c>
       <c r="M25" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>{'n_estimators': 100, 'max_depth': 3, 'learning_rate': 0.010419273652354186}</t>
+          <t>{'n_estimators': 295, 'max_depth': 4, 'learning_rate': 0.15462580436171433}</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="P25" t="n">
-        <v>1</v>
+        <v>0.8649350649350649</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.01</v>
+        <v>0.6</v>
       </c>
       <c r="D26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F26" t="n">
         <v>20</v>
       </c>
       <c r="G26" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -1937,52 +1937,52 @@
         </is>
       </c>
       <c r="J26" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="K26" t="n">
-        <v>0.95</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="L26" t="n">
-        <v>0.9503836317135551</v>
+        <v>0.9321387790953009</v>
       </c>
       <c r="M26" t="n">
-        <v>0.11</v>
+        <v>0.23</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>{'n_estimators': 356, 'max_depth': 17, 'learning_rate': 0.18534002373486191}</t>
+          <t>{'n_estimators': 215, 'max_depth': 4, 'learning_rate': 0.19112534013992316}</t>
         </is>
       </c>
       <c r="O26" t="n">
-        <v>0.95</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P26" t="n">
-        <v>0.9503836317135551</v>
+        <v>0.9321387790953009</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.01</v>
+        <v>0.58</v>
       </c>
       <c r="D27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F27" t="n">
         <v>20</v>
       </c>
       <c r="G27" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -1995,52 +1995,52 @@
         </is>
       </c>
       <c r="J27" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0.8976608187134503</v>
       </c>
       <c r="M27" t="n">
-        <v>0.05</v>
+        <v>0.28</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>{'n_estimators': 99, 'max_depth': 9, 'learning_rate': 0.1921144028381138}</t>
+          <t>{'n_estimators': 260, 'max_depth': 16, 'learning_rate': 0.28297415187835673}</t>
         </is>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>0.9333333333333333</v>
       </c>
       <c r="P27" t="n">
-        <v>1</v>
+        <v>0.9325641025641026</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.01</v>
+        <v>0.5</v>
       </c>
       <c r="D28" t="n">
         <v>16</v>
       </c>
       <c r="E28" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F28" t="n">
         <v>20</v>
       </c>
       <c r="G28" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2053,52 +2053,52 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>0.7297364672364672</v>
       </c>
       <c r="M28" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>{'n_estimators': 75, 'max_depth': 13, 'learning_rate': 0.0350274607073846}</t>
+          <t>{'n_estimators': 51, 'max_depth': 14, 'learning_rate': 0.0636648327379371}</t>
         </is>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0.7297364672364672</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.01</v>
+        <v>0.54</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F29" t="n">
         <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         </is>
       </c>
       <c r="J29" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="K29" t="n">
         <v>1</v>
@@ -2120,11 +2120,11 @@
         <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>{'n_estimators': 301, 'max_depth': 5, 'learning_rate': 0.26887255070221444}</t>
+          <t>{'n_estimators': 309, 'max_depth': 16, 'learning_rate': 0.01650838400437187}</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -2136,27 +2136,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Oui (DDBS - euclidean, geometric)</t>
+          <t>Oui (GMM)</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.01</v>
+        <v>0.51</v>
       </c>
       <c r="D30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E30" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F30" t="n">
         <v>20</v>
       </c>
       <c r="G30" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2169,85 +2169,5215 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="K30" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="L30" t="n">
-        <v>1</v>
+        <v>0.9670531400966184</v>
       </c>
       <c r="M30" t="n">
-        <v>0.09</v>
+        <v>0.28</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>{'n_estimators': 271, 'max_depth': 5, 'learning_rate': 0.1207355004384379}</t>
+          <t>{'n_estimators': 272, 'max_depth': 6, 'learning_rate': 0.01591419839722443}</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>1</v>
+        <v>0.9666666666666667</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0.9670531400966184</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Oui (GMM)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="D31" t="n">
+        <v>16</v>
+      </c>
+      <c r="E31" t="n">
+        <v>24</v>
+      </c>
+      <c r="F31" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" t="n">
+        <v>30</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.8637037037037038</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 219, 'max_depth': 10, 'learning_rate': 0.049858956141912554}</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.8637037037037038</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>1</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>80</v>
+      </c>
+      <c r="E32" t="n">
+        <v>120</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 164, 'max_depth': 14, 'learning_rate': 0.10751910722771531}</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>1</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>80</v>
+      </c>
+      <c r="E33" t="n">
+        <v>120</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" t="n">
+        <v>30</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9347222222222221</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 149, 'max_depth': 11, 'learning_rate': 0.16551860720125233}</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.967111111111111</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>80</v>
+      </c>
+      <c r="E34" t="n">
+        <v>120</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" t="n">
+        <v>30</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.9667698658410733</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 73, 'max_depth': 7, 'learning_rate': 0.01072195537139369}</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>4</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>80</v>
+      </c>
+      <c r="E35" t="n">
+        <v>120</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" t="n">
+        <v>30</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.8634252297410191</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 153, 'max_depth': 13, 'learning_rate': 0.021972642838304076}</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.8962322472848789</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>80</v>
+      </c>
+      <c r="E36" t="n">
+        <v>120</v>
+      </c>
+      <c r="F36" t="n">
+        <v>20</v>
+      </c>
+      <c r="G36" t="n">
+        <v>30</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.9668771929824561</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 218, 'max_depth': 13, 'learning_rate': 0.019256065517300105}</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.9668771929824561</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>6</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>80</v>
+      </c>
+      <c r="E37" t="n">
+        <v>120</v>
+      </c>
+      <c r="F37" t="n">
+        <v>20</v>
+      </c>
+      <c r="G37" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.9671604938271604</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 98, 'max_depth': 9, 'learning_rate': 0.012763642107845074}</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>7</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>80</v>
+      </c>
+      <c r="E38" t="n">
+        <v>120</v>
+      </c>
+      <c r="F38" t="n">
+        <v>20</v>
+      </c>
+      <c r="G38" t="n">
+        <v>30</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.9669841269841268</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 138, 'max_depth': 7, 'learning_rate': 0.2437248683698474}</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.9669841269841268</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>8</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>80</v>
+      </c>
+      <c r="E39" t="n">
+        <v>120</v>
+      </c>
+      <c r="F39" t="n">
+        <v>20</v>
+      </c>
+      <c r="G39" t="n">
+        <v>30</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.9351190476190477</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 360, 'max_depth': 4, 'learning_rate': 0.04068127683800077}</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.9351190476190477</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>9</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>80</v>
+      </c>
+      <c r="E40" t="n">
+        <v>120</v>
+      </c>
+      <c r="F40" t="n">
+        <v>20</v>
+      </c>
+      <c r="G40" t="n">
+        <v>30</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.9014652014652015</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 286, 'max_depth': 8, 'learning_rate': 0.06411946406434042}</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.9014652014652015</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>10</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>80</v>
+      </c>
+      <c r="E41" t="n">
+        <v>120</v>
+      </c>
+      <c r="F41" t="n">
+        <v>20</v>
+      </c>
+      <c r="G41" t="n">
+        <v>30</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.967644183773216</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 174, 'max_depth': 20, 'learning_rate': 0.03155518490595779}</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.967644183773216</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>11</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>80</v>
+      </c>
+      <c r="E42" t="n">
+        <v>120</v>
+      </c>
+      <c r="F42" t="n">
+        <v>20</v>
+      </c>
+      <c r="G42" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 393, 'max_depth': 12, 'learning_rate': 0.04332638262334696}</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>12</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>80</v>
+      </c>
+      <c r="E43" t="n">
+        <v>120</v>
+      </c>
+      <c r="F43" t="n">
+        <v>20</v>
+      </c>
+      <c r="G43" t="n">
+        <v>30</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.898093058733791</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 198, 'max_depth': 19, 'learning_rate': 0.011057029431661468}</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.9312314602932453</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>13</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>80</v>
+      </c>
+      <c r="E44" t="n">
+        <v>120</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20</v>
+      </c>
+      <c r="G44" t="n">
+        <v>30</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.8218796992481202</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 307, 'max_depth': 2, 'learning_rate': 0.045481059995257714}</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8218796992481202</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>14</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>80</v>
+      </c>
+      <c r="E45" t="n">
+        <v>120</v>
+      </c>
+      <c r="F45" t="n">
+        <v>20</v>
+      </c>
+      <c r="G45" t="n">
+        <v>30</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.8312169312169312</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 71, 'max_depth': 10, 'learning_rate': 0.013124560937066296}</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.8648351648351648</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
         <v>15</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>80</v>
+      </c>
+      <c r="E46" t="n">
+        <v>120</v>
+      </c>
+      <c r="F46" t="n">
+        <v>20</v>
+      </c>
+      <c r="G46" t="n">
+        <v>30</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.8627384960718294</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 127, 'max_depth': 8, 'learning_rate': 0.013408592084628178}</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.9318993352326685</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>16</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>80</v>
+      </c>
+      <c r="E47" t="n">
+        <v>120</v>
+      </c>
+      <c r="F47" t="n">
+        <v>20</v>
+      </c>
+      <c r="G47" t="n">
+        <v>30</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.9003220611916264</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 134, 'max_depth': 13, 'learning_rate': 0.02806171014106945}</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>17</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>80</v>
+      </c>
+      <c r="E48" t="n">
+        <v>120</v>
+      </c>
+      <c r="F48" t="n">
+        <v>20</v>
+      </c>
+      <c r="G48" t="n">
+        <v>30</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.8983908045977013</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 95, 'max_depth': 6, 'learning_rate': 0.016709315615579787}</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.9670297748729122</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>18</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>80</v>
+      </c>
+      <c r="E49" t="n">
+        <v>120</v>
+      </c>
+      <c r="F49" t="n">
+        <v>20</v>
+      </c>
+      <c r="G49" t="n">
+        <v>30</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.9665634674922601</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 110, 'max_depth': 20, 'learning_rate': 0.19678493904380293}</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.9665634674922601</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>19</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>80</v>
+      </c>
+      <c r="E50" t="n">
+        <v>120</v>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
+      </c>
+      <c r="G50" t="n">
+        <v>30</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 120, 'max_depth': 9, 'learning_rate': 0.022787249761239806}</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>1</v>
+      </c>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>20</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>80</v>
+      </c>
+      <c r="E51" t="n">
+        <v>120</v>
+      </c>
+      <c r="F51" t="n">
+        <v>20</v>
+      </c>
+      <c r="G51" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.8997493734335839</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 431, 'max_depth': 9, 'learning_rate': 0.030880709704094865}</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.8997493734335839</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>21</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>80</v>
+      </c>
+      <c r="E52" t="n">
+        <v>120</v>
+      </c>
+      <c r="F52" t="n">
+        <v>20</v>
+      </c>
+      <c r="G52" t="n">
+        <v>30</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.9663529411764706</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 251, 'max_depth': 20, 'learning_rate': 0.242086320653762}</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.9663529411764706</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>22</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>80</v>
+      </c>
+      <c r="E53" t="n">
+        <v>120</v>
+      </c>
+      <c r="F53" t="n">
+        <v>20</v>
+      </c>
+      <c r="G53" t="n">
+        <v>30</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.9665976535541752</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 235, 'max_depth': 17, 'learning_rate': 0.016566111448745372}</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>1</v>
+      </c>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>23</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>80</v>
+      </c>
+      <c r="E54" t="n">
+        <v>120</v>
+      </c>
+      <c r="F54" t="n">
+        <v>20</v>
+      </c>
+      <c r="G54" t="n">
+        <v>30</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 272, 'max_depth': 11, 'learning_rate': 0.011140014464377094}</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>1</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>24</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>80</v>
+      </c>
+      <c r="E55" t="n">
+        <v>120</v>
+      </c>
+      <c r="F55" t="n">
+        <v>20</v>
+      </c>
+      <c r="G55" t="n">
+        <v>30</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.9671550671550672</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 205, 'max_depth': 8, 'learning_rate': 0.20017460950554428}</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.9671550671550672</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>25</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>80</v>
+      </c>
+      <c r="E56" t="n">
+        <v>120</v>
+      </c>
+      <c r="F56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G56" t="n">
+        <v>30</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.9347222222222221</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 481, 'max_depth': 10, 'learning_rate': 0.03493016035288508}</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.9347222222222221</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>26</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>80</v>
+      </c>
+      <c r="E57" t="n">
+        <v>120</v>
+      </c>
+      <c r="F57" t="n">
+        <v>20</v>
+      </c>
+      <c r="G57" t="n">
+        <v>30</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 452, 'max_depth': 18, 'learning_rate': 0.05553889601942097}</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>27</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>80</v>
+      </c>
+      <c r="E58" t="n">
+        <v>120</v>
+      </c>
+      <c r="F58" t="n">
+        <v>20</v>
+      </c>
+      <c r="G58" t="n">
+        <v>30</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 267, 'max_depth': 10, 'learning_rate': 0.18447198102041007}</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>1</v>
+      </c>
+      <c r="P58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>28</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>80</v>
+      </c>
+      <c r="E59" t="n">
+        <v>120</v>
+      </c>
+      <c r="F59" t="n">
+        <v>20</v>
+      </c>
+      <c r="G59" t="n">
+        <v>30</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 388, 'max_depth': 19, 'learning_rate': 0.030760711605194488}</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>29</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>80</v>
+      </c>
+      <c r="E60" t="n">
+        <v>120</v>
+      </c>
+      <c r="F60" t="n">
+        <v>20</v>
+      </c>
+      <c r="G60" t="n">
+        <v>30</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.9341818181818181</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 457, 'max_depth': 4, 'learning_rate': 0.12036418045590307}</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.9341818181818181</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>30</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Non</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>80</v>
+      </c>
+      <c r="E61" t="n">
+        <v>120</v>
+      </c>
+      <c r="F61" t="n">
+        <v>20</v>
+      </c>
+      <c r="G61" t="n">
+        <v>30</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K61" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 352, 'max_depth': 8, 'learning_rate': 0.018353392640058128}</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>1</v>
+      </c>
+      <c r="P61" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>1</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" t="n">
+        <v>16</v>
+      </c>
+      <c r="E62" t="n">
+        <v>24</v>
+      </c>
+      <c r="F62" t="n">
+        <v>20</v>
+      </c>
+      <c r="G62" t="n">
+        <v>30</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.8049999999999999</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 242, 'max_depth': 10, 'learning_rate': 0.011709290124876781}</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.8680952380952381</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" t="n">
+        <v>16</v>
+      </c>
+      <c r="E63" t="n">
+        <v>24</v>
+      </c>
+      <c r="F63" t="n">
+        <v>20</v>
+      </c>
+      <c r="G63" t="n">
+        <v>30</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.9665976535541753</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 241, 'max_depth': 14, 'learning_rate': 0.2664471833745751}</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.9665976535541753</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>16</v>
+      </c>
+      <c r="E64" t="n">
+        <v>24</v>
+      </c>
+      <c r="F64" t="n">
+        <v>20</v>
+      </c>
+      <c r="G64" t="n">
+        <v>30</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.8991658066735465</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 189, 'max_depth': 13, 'learning_rate': 0.020761717599248195}</t>
+        </is>
+      </c>
+      <c r="O64" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.8991658066735465</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>4</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" t="n">
+        <v>16</v>
+      </c>
+      <c r="E65" t="n">
+        <v>24</v>
+      </c>
+      <c r="F65" t="n">
+        <v>20</v>
+      </c>
+      <c r="G65" t="n">
+        <v>30</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.7003174603174603</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 54, 'max_depth': 12, 'learning_rate': 0.010151940802600665}</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.7746031746031746</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>5</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" t="n">
+        <v>16</v>
+      </c>
+      <c r="E66" t="n">
+        <v>24</v>
+      </c>
+      <c r="F66" t="n">
+        <v>20</v>
+      </c>
+      <c r="G66" t="n">
+        <v>30</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.9321937321937322</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 62, 'max_depth': 14, 'learning_rate': 0.017765348914516595}</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>1</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>6</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" t="n">
+        <v>16</v>
+      </c>
+      <c r="E67" t="n">
+        <v>24</v>
+      </c>
+      <c r="F67" t="n">
+        <v>20</v>
+      </c>
+      <c r="G67" t="n">
+        <v>30</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.9330734243014944</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 456, 'max_depth': 14, 'learning_rate': 0.06471681596721991}</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.9330734243014944</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>7</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" t="n">
+        <v>16</v>
+      </c>
+      <c r="E68" t="n">
+        <v>24</v>
+      </c>
+      <c r="F68" t="n">
+        <v>20</v>
+      </c>
+      <c r="G68" t="n">
+        <v>30</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.7956011396011395</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 471, 'max_depth': 8, 'learning_rate': 0.0570482408178198}</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.7956011396011395</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>8</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" t="n">
+        <v>16</v>
+      </c>
+      <c r="E69" t="n">
+        <v>24</v>
+      </c>
+      <c r="F69" t="n">
+        <v>20</v>
+      </c>
+      <c r="G69" t="n">
+        <v>30</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.894831441348469</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 77, 'max_depth': 3, 'learning_rate': 0.02027245859605764}</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.894831441348469</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>9</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" t="n">
+        <v>16</v>
+      </c>
+      <c r="E70" t="n">
+        <v>24</v>
+      </c>
+      <c r="F70" t="n">
+        <v>20</v>
+      </c>
+      <c r="G70" t="n">
+        <v>30</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 57, 'max_depth': 7, 'learning_rate': 0.017435302087710068}</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>10</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" t="n">
+        <v>16</v>
+      </c>
+      <c r="E71" t="n">
+        <v>24</v>
+      </c>
+      <c r="F71" t="n">
+        <v>20</v>
+      </c>
+      <c r="G71" t="n">
+        <v>30</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1</v>
+      </c>
+      <c r="L71" t="n">
+        <v>1</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 134, 'max_depth': 17, 'learning_rate': 0.02013496776072105}</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>11</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" t="n">
+        <v>16</v>
+      </c>
+      <c r="E72" t="n">
+        <v>24</v>
+      </c>
+      <c r="F72" t="n">
+        <v>20</v>
+      </c>
+      <c r="G72" t="n">
+        <v>30</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 203, 'max_depth': 2, 'learning_rate': 0.09689751032492888}</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>12</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" t="n">
+        <v>16</v>
+      </c>
+      <c r="E73" t="n">
+        <v>24</v>
+      </c>
+      <c r="F73" t="n">
+        <v>20</v>
+      </c>
+      <c r="G73" t="n">
+        <v>30</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.9305555555555555</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 216, 'max_depth': 18, 'learning_rate': 0.14874695900423276}</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.9305555555555555</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>13</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" t="n">
+        <v>16</v>
+      </c>
+      <c r="E74" t="n">
+        <v>24</v>
+      </c>
+      <c r="F74" t="n">
+        <v>20</v>
+      </c>
+      <c r="G74" t="n">
+        <v>30</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.8644444444444446</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 247, 'max_depth': 12, 'learning_rate': 0.012033015178496125}</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.8644444444444446</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>14</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" t="n">
+        <v>16</v>
+      </c>
+      <c r="E75" t="n">
+        <v>24</v>
+      </c>
+      <c r="F75" t="n">
+        <v>20</v>
+      </c>
+      <c r="G75" t="n">
+        <v>30</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9018947368421053</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 203, 'max_depth': 10, 'learning_rate': 0.2872477179397138}</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.9018947368421053</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>15</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="D76" t="n">
+        <v>16</v>
+      </c>
+      <c r="E76" t="n">
+        <v>24</v>
+      </c>
+      <c r="F76" t="n">
+        <v>20</v>
+      </c>
+      <c r="G76" t="n">
+        <v>30</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.8636190476190476</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 211, 'max_depth': 17, 'learning_rate': 0.1461401345792447}</t>
+        </is>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.8636190476190476</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>16</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" t="n">
+        <v>16</v>
+      </c>
+      <c r="E77" t="n">
+        <v>24</v>
+      </c>
+      <c r="F77" t="n">
+        <v>20</v>
+      </c>
+      <c r="G77" t="n">
+        <v>30</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.8689458689458689</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 129, 'max_depth': 17, 'learning_rate': 0.0734273693512239}</t>
+        </is>
+      </c>
+      <c r="O77" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.8689458689458689</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>17</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" t="n">
+        <v>16</v>
+      </c>
+      <c r="E78" t="n">
+        <v>24</v>
+      </c>
+      <c r="F78" t="n">
+        <v>20</v>
+      </c>
+      <c r="G78" t="n">
+        <v>30</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.8636658141517477</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 256, 'max_depth': 19, 'learning_rate': 0.04145956828158375}</t>
+        </is>
+      </c>
+      <c r="O78" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.8636658141517477</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>18</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>16</v>
+      </c>
+      <c r="E79" t="n">
+        <v>24</v>
+      </c>
+      <c r="F79" t="n">
+        <v>20</v>
+      </c>
+      <c r="G79" t="n">
+        <v>30</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.6932992327365729</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 131, 'max_depth': 19, 'learning_rate': 0.01374029693400804}</t>
+        </is>
+      </c>
+      <c r="O79" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.6932992327365729</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>19</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0</v>
+      </c>
+      <c r="D80" t="n">
+        <v>16</v>
+      </c>
+      <c r="E80" t="n">
+        <v>24</v>
+      </c>
+      <c r="F80" t="n">
+        <v>20</v>
+      </c>
+      <c r="G80" t="n">
+        <v>30</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.9662618083670715</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 385, 'max_depth': 9, 'learning_rate': 0.20487255008210534}</t>
+        </is>
+      </c>
+      <c r="O80" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.9662618083670715</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>20</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" t="n">
+        <v>16</v>
+      </c>
+      <c r="E81" t="n">
+        <v>24</v>
+      </c>
+      <c r="F81" t="n">
+        <v>20</v>
+      </c>
+      <c r="G81" t="n">
+        <v>30</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.9281521093285799</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 203, 'max_depth': 6, 'learning_rate': 0.039071833300212674}</t>
+        </is>
+      </c>
+      <c r="O81" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.9281521093285799</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>21</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>16</v>
+      </c>
+      <c r="E82" t="n">
+        <v>24</v>
+      </c>
+      <c r="F82" t="n">
+        <v>20</v>
+      </c>
+      <c r="G82" t="n">
+        <v>30</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.9328395061728396</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 399, 'max_depth': 18, 'learning_rate': 0.03627586107488362}</t>
+        </is>
+      </c>
+      <c r="O82" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.9328395061728396</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>22</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" t="n">
+        <v>16</v>
+      </c>
+      <c r="E83" t="n">
+        <v>24</v>
+      </c>
+      <c r="F83" t="n">
+        <v>20</v>
+      </c>
+      <c r="G83" t="n">
+        <v>30</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.9321969696969696</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 241, 'max_depth': 15, 'learning_rate': 0.07066981654398387}</t>
+        </is>
+      </c>
+      <c r="O83" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0.9664799253034547</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>23</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" t="n">
+        <v>16</v>
+      </c>
+      <c r="E84" t="n">
+        <v>24</v>
+      </c>
+      <c r="F84" t="n">
+        <v>20</v>
+      </c>
+      <c r="G84" t="n">
+        <v>30</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.9665976535541752</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 366, 'max_depth': 17, 'learning_rate': 0.0139009105785802}</t>
+        </is>
+      </c>
+      <c r="O84" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.9665976535541752</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>24</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" t="n">
+        <v>16</v>
+      </c>
+      <c r="E85" t="n">
+        <v>24</v>
+      </c>
+      <c r="F85" t="n">
+        <v>20</v>
+      </c>
+      <c r="G85" t="n">
+        <v>30</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 314, 'max_depth': 3, 'learning_rate': 0.03155489980751563}</t>
+        </is>
+      </c>
+      <c r="O85" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>25</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" t="n">
+        <v>16</v>
+      </c>
+      <c r="E86" t="n">
+        <v>24</v>
+      </c>
+      <c r="F86" t="n">
+        <v>20</v>
+      </c>
+      <c r="G86" t="n">
+        <v>30</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.8994243510372543</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 325, 'max_depth': 5, 'learning_rate': 0.08222165522346137}</t>
+        </is>
+      </c>
+      <c r="O86" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.8994243510372543</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>26</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" t="n">
+        <v>16</v>
+      </c>
+      <c r="E87" t="n">
+        <v>24</v>
+      </c>
+      <c r="F87" t="n">
+        <v>20</v>
+      </c>
+      <c r="G87" t="n">
+        <v>30</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.9665141113653699</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 311, 'max_depth': 17, 'learning_rate': 0.023640441018198767}</t>
+        </is>
+      </c>
+      <c r="O87" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.9665141113653699</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>27</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" t="n">
+        <v>16</v>
+      </c>
+      <c r="E88" t="n">
+        <v>24</v>
+      </c>
+      <c r="F88" t="n">
+        <v>20</v>
+      </c>
+      <c r="G88" t="n">
+        <v>30</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.9015204678362572</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 491, 'max_depth': 12, 'learning_rate': 0.020439852723463096}</t>
+        </is>
+      </c>
+      <c r="O88" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.9015204678362572</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>28</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" t="n">
+        <v>16</v>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="n">
+        <v>20</v>
+      </c>
+      <c r="G89" t="n">
+        <v>30</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.7531400966183575</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 373, 'max_depth': 9, 'learning_rate': 0.29800497224025235}</t>
+        </is>
+      </c>
+      <c r="O89" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.7531400966183575</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>29</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" t="n">
+        <v>16</v>
+      </c>
+      <c r="E90" t="n">
+        <v>24</v>
+      </c>
+      <c r="F90" t="n">
+        <v>20</v>
+      </c>
+      <c r="G90" t="n">
+        <v>30</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.9667936507936508</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 356, 'max_depth': 17, 'learning_rate': 0.02976150057777681}</t>
+        </is>
+      </c>
+      <c r="O90" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.9667936507936508</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>30</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Oui (Random)</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" t="n">
+        <v>16</v>
+      </c>
+      <c r="E91" t="n">
+        <v>24</v>
+      </c>
+      <c r="F91" t="n">
+        <v>20</v>
+      </c>
+      <c r="G91" t="n">
+        <v>30</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.900250626566416</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 159, 'max_depth': 2, 'learning_rate': 0.060231637557384594}</t>
+        </is>
+      </c>
+      <c r="O91" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.900250626566416</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" t="inlineStr">
         <is>
           <t>Oui (DDBS - euclidean, geometric)</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C92" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D92" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E92" t="n">
+        <v>23</v>
+      </c>
+      <c r="F92" t="n">
+        <v>20</v>
+      </c>
+      <c r="G92" t="n">
+        <v>30</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 116, 'max_depth': 5, 'learning_rate': 0.039925533432234026}</t>
+        </is>
+      </c>
+      <c r="O92" t="n">
+        <v>1</v>
+      </c>
+      <c r="P92" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
         <v>0.01</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D93" t="n">
+        <v>16</v>
+      </c>
+      <c r="E93" t="n">
+        <v>24</v>
+      </c>
+      <c r="F93" t="n">
+        <v>20</v>
+      </c>
+      <c r="G93" t="n">
+        <v>30</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 348, 'max_depth': 3, 'learning_rate': 0.04849654938065925}</t>
+        </is>
+      </c>
+      <c r="O93" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D94" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E94" t="n">
+        <v>22</v>
+      </c>
+      <c r="F94" t="n">
+        <v>20</v>
+      </c>
+      <c r="G94" t="n">
+        <v>30</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.9021052631578947</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 334, 'max_depth': 14, 'learning_rate': 0.03571088539690878}</t>
+        </is>
+      </c>
+      <c r="O94" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.9021052631578947</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>4</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D95" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E95" t="n">
+        <v>23</v>
+      </c>
+      <c r="F95" t="n">
+        <v>20</v>
+      </c>
+      <c r="G95" t="n">
+        <v>30</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 202, 'max_depth': 18, 'learning_rate': 0.01266532202420994}</t>
+        </is>
+      </c>
+      <c r="O95" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>5</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D96" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23</v>
+      </c>
+      <c r="F96" t="n">
+        <v>20</v>
+      </c>
+      <c r="G96" t="n">
+        <v>30</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.9329276538201489</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 310, 'max_depth': 4, 'learning_rate': 0.09037287160968761}</t>
+        </is>
+      </c>
+      <c r="O96" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.9329276538201489</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>6</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D97" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E97" t="n">
+        <v>22</v>
+      </c>
+      <c r="F97" t="n">
+        <v>20</v>
+      </c>
+      <c r="G97" t="n">
+        <v>30</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.791843137254902</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 354, 'max_depth': 20, 'learning_rate': 0.07517310556188106}</t>
+        </is>
+      </c>
+      <c r="O97" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.791843137254902</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>7</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D98" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E98" t="n">
+        <v>22</v>
+      </c>
+      <c r="F98" t="n">
+        <v>20</v>
+      </c>
+      <c r="G98" t="n">
+        <v>30</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.9665976535541752</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 80, 'max_depth': 16, 'learning_rate': 0.20822643180134845}</t>
+        </is>
+      </c>
+      <c r="O98" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.9665976535541752</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>8</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D99" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E99" t="n">
+        <v>23</v>
+      </c>
+      <c r="F99" t="n">
+        <v>20</v>
+      </c>
+      <c r="G99" t="n">
+        <v>30</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.9663529411764705</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 434, 'max_depth': 9, 'learning_rate': 0.015520568059843667}</t>
+        </is>
+      </c>
+      <c r="O99" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.9663529411764705</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>9</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>16</v>
+      </c>
+      <c r="E100" t="n">
+        <v>24</v>
+      </c>
+      <c r="F100" t="n">
+        <v>20</v>
+      </c>
+      <c r="G100" t="n">
+        <v>30</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.9673046251993621</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 100, 'max_depth': 20, 'learning_rate': 0.09009004671313021}</t>
+        </is>
+      </c>
+      <c r="O100" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.9673046251993621</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>10</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E101" t="n">
+        <v>23</v>
+      </c>
+      <c r="F101" t="n">
+        <v>20</v>
+      </c>
+      <c r="G101" t="n">
+        <v>30</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.8999999999999999</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 363, 'max_depth': 2, 'learning_rate': 0.03846094642320337}</t>
+        </is>
+      </c>
+      <c r="O101" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>11</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D102" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E102" t="n">
+        <v>22</v>
+      </c>
+      <c r="F102" t="n">
+        <v>20</v>
+      </c>
+      <c r="G102" t="n">
+        <v>30</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 483, 'max_depth': 4, 'learning_rate': 0.0791760884375733}</t>
+        </is>
+      </c>
+      <c r="O102" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>12</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D103" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E103" t="n">
+        <v>22</v>
+      </c>
+      <c r="F103" t="n">
+        <v>20</v>
+      </c>
+      <c r="G103" t="n">
+        <v>30</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.9668534080298786</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 441, 'max_depth': 4, 'learning_rate': 0.07492994357718817}</t>
+        </is>
+      </c>
+      <c r="O103" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.9668534080298786</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>13</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D104" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E104" t="n">
+        <v>22</v>
+      </c>
+      <c r="F104" t="n">
+        <v>20</v>
+      </c>
+      <c r="G104" t="n">
+        <v>30</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 488, 'max_depth': 11, 'learning_rate': 0.04540120095736756}</t>
+        </is>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>14</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D105" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E105" t="n">
+        <v>22</v>
+      </c>
+      <c r="F105" t="n">
+        <v>20</v>
+      </c>
+      <c r="G105" t="n">
+        <v>30</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.966837606837607</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 109, 'max_depth': 12, 'learning_rate': 0.052079973166699926}</t>
+        </is>
+      </c>
+      <c r="O105" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.966837606837607</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
         <v>15</v>
       </c>
-      <c r="E31" t="n">
-        <v>15</v>
-      </c>
-      <c r="F31" t="n">
-        <v>20</v>
-      </c>
-      <c r="G31" t="n">
-        <v>20</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
-        </is>
-      </c>
-      <c r="J31" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="K31" t="n">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D106" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E106" t="n">
+        <v>23</v>
+      </c>
+      <c r="F106" t="n">
+        <v>20</v>
+      </c>
+      <c r="G106" t="n">
+        <v>30</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.9336363636363636</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 123, 'max_depth': 19, 'learning_rate': 0.10946955728847188}</t>
+        </is>
+      </c>
+      <c r="O106" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0.9336363636363636</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>16</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D107" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E107" t="n">
+        <v>23</v>
+      </c>
+      <c r="F107" t="n">
+        <v>20</v>
+      </c>
+      <c r="G107" t="n">
+        <v>30</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.899047619047619</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 208, 'max_depth': 4, 'learning_rate': 0.013852741265365813}</t>
+        </is>
+      </c>
+      <c r="O107" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.9316017316017315</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>17</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E108" t="n">
+        <v>22</v>
+      </c>
+      <c r="F108" t="n">
+        <v>20</v>
+      </c>
+      <c r="G108" t="n">
+        <v>30</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.9353174603174602</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 148, 'max_depth': 9, 'learning_rate': 0.10337456992472369}</t>
+        </is>
+      </c>
+      <c r="O108" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.9353174603174602</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>18</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E109" t="n">
+        <v>22</v>
+      </c>
+      <c r="F109" t="n">
+        <v>20</v>
+      </c>
+      <c r="G109" t="n">
+        <v>30</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.9660512820512821</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 197, 'max_depth': 20, 'learning_rate': 0.12788533239150698}</t>
+        </is>
+      </c>
+      <c r="O109" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.9660512820512821</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>19</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D110" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E110" t="n">
+        <v>23</v>
+      </c>
+      <c r="F110" t="n">
+        <v>20</v>
+      </c>
+      <c r="G110" t="n">
+        <v>30</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 297, 'max_depth': 14, 'learning_rate': 0.13674131010714677}</t>
+        </is>
+      </c>
+      <c r="O110" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="n">
+      <c r="P110" t="n">
         <v>1</v>
       </c>
-      <c r="M31" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>{'n_estimators': 490, 'max_depth': 16, 'learning_rate': 0.03538301071787787}</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1</v>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>20</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D111" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E111" t="n">
+        <v>23</v>
+      </c>
+      <c r="F111" t="n">
+        <v>20</v>
+      </c>
+      <c r="G111" t="n">
+        <v>30</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.9340067340067341</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 430, 'max_depth': 15, 'learning_rate': 0.0536037283146596}</t>
+        </is>
+      </c>
+      <c r="O111" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.96692242114237</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>21</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D112" t="n">
+        <v>16</v>
+      </c>
+      <c r="E112" t="n">
+        <v>24</v>
+      </c>
+      <c r="F112" t="n">
+        <v>20</v>
+      </c>
+      <c r="G112" t="n">
+        <v>30</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.9665831244778613</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 85, 'max_depth': 11, 'learning_rate': 0.08965100460398964}</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.9665831244778613</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>22</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D113" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E113" t="n">
+        <v>23</v>
+      </c>
+      <c r="F113" t="n">
+        <v>20</v>
+      </c>
+      <c r="G113" t="n">
+        <v>30</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.9660018993352326</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 455, 'max_depth': 12, 'learning_rate': 0.28847050874119184}</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.9660018993352326</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>23</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D114" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E114" t="n">
+        <v>23</v>
+      </c>
+      <c r="F114" t="n">
+        <v>20</v>
+      </c>
+      <c r="G114" t="n">
+        <v>30</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J114" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.9668192219679634</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 389, 'max_depth': 17, 'learning_rate': 0.030697698821046695}</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.9668192219679634</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>24</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D115" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E115" t="n">
+        <v>23</v>
+      </c>
+      <c r="F115" t="n">
+        <v>20</v>
+      </c>
+      <c r="G115" t="n">
+        <v>30</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J115" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 79, 'max_depth': 6, 'learning_rate': 0.1387838745560815}</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>25</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D116" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E116" t="n">
+        <v>23</v>
+      </c>
+      <c r="F116" t="n">
+        <v>20</v>
+      </c>
+      <c r="G116" t="n">
+        <v>30</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.9660018993352326</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 419, 'max_depth': 16, 'learning_rate': 0.16952042781587462}</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.9660018993352326</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>26</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E117" t="n">
+        <v>23</v>
+      </c>
+      <c r="F117" t="n">
+        <v>20</v>
+      </c>
+      <c r="G117" t="n">
+        <v>30</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J117" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.900331041507512</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 499, 'max_depth': 17, 'learning_rate': 0.040097172964713164}</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.900331041507512</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>27</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D118" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E118" t="n">
+        <v>23</v>
+      </c>
+      <c r="F118" t="n">
+        <v>20</v>
+      </c>
+      <c r="G118" t="n">
+        <v>30</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J118" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.8363605091159271</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 215, 'max_depth': 19, 'learning_rate': 0.013588760107486086}</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.8363605091159271</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>28</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E119" t="n">
+        <v>22</v>
+      </c>
+      <c r="F119" t="n">
+        <v>20</v>
+      </c>
+      <c r="G119" t="n">
+        <v>30</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.9350649350649349</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 438, 'max_depth': 8, 'learning_rate': 0.22750834702132317}</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.9350649350649349</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>29</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D120" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="E120" t="n">
+        <v>22</v>
+      </c>
+      <c r="F120" t="n">
+        <v>20</v>
+      </c>
+      <c r="G120" t="n">
+        <v>30</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.9672727272727272</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 91, 'max_depth': 20, 'learning_rate': 0.08541284998290748}</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>0.9666666666666667</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.9672727272727272</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>30</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Oui (DDBS - euclidean, geometric)</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D121" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="E121" t="n">
+        <v>23</v>
+      </c>
+      <c r="F121" t="n">
+        <v>20</v>
+      </c>
+      <c r="G121" t="n">
+        <v>30</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>{'learning_rate': 0.1, 'max_depth': 6, 'n_estimators': 100}</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.864</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>{'n_estimators': 400, 'max_depth': 4, 'learning_rate': 0.05907635880186167}</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.864</v>
       </c>
     </row>
   </sheetData>
